--- a/example.xlsx
+++ b/example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beribeli/Workarea/irgen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDC6A2C-06DB-BC44-864A-2FEB24C3347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA98CC92-D634-614C-8090-C66DDF59DAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
   <si>
     <t>VENDOR</t>
   </si>
@@ -198,6 +198,18 @@
   </si>
   <si>
     <t>regb{n}, n=range(0, 2, 8)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[63:0]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rege{n}, n=range(0, 2, 8)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -257,10 +269,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -598,10 +610,10 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -622,8 +634,8 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
@@ -642,8 +654,8 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
@@ -662,8 +674,8 @@
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
@@ -754,10 +766,10 @@
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -778,8 +790,8 @@
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
@@ -817,7 +829,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="7.1640625" style="1" customWidth="1"/>
@@ -879,10 +891,10 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -902,8 +914,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
@@ -921,8 +933,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
@@ -940,8 +952,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1028,7 +1040,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -1051,8 +1063,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1070,10 +1082,10 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1093,8 +1105,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1115,7 +1127,7 @@
       <c r="A14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1128,6 +1140,26 @@
         <v>27</v>
       </c>
       <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="1">
+        <v>64</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="1">
         <v>0</v>
       </c>
     </row>

--- a/example.xlsx
+++ b/example.xlsx
@@ -463,8 +463,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DESC</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -511,8 +513,10 @@
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DESC</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -550,28 +554,29 @@
   <cols>
     <col min="1" max="1" width="7.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>REG_DESC</t>
+        </is>
+      </c>
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>22</v>
@@ -579,8 +584,10 @@
       <c r="G1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FIELD_DESC</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -590,14 +597,11 @@
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="1">
-        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>27</v>
@@ -616,14 +620,11 @@
       <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E3" s="1">
-        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>34</v>
@@ -636,14 +637,11 @@
     <row r="4" spans="1:8">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" s="1">
-        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>27</v>
@@ -656,14 +654,11 @@
     <row r="5" spans="1:8">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" s="1">
-        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>34</v>
@@ -676,14 +671,11 @@
     <row r="6" spans="1:8">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E6" s="1">
-        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>27</v>
@@ -700,14 +692,11 @@
       <c r="B7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" s="1">
-        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>42</v>
@@ -724,14 +713,11 @@
       <c r="B8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="1">
-        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
@@ -748,14 +734,11 @@
       <c r="B9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E9" s="1">
-        <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>27</v>
@@ -772,14 +755,11 @@
       <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E10" s="1">
-        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>27</v>
@@ -792,14 +772,11 @@
     <row r="11" spans="1:8">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E11" s="1">
-        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>27</v>
@@ -834,28 +811,30 @@
   <cols>
     <col min="1" max="1" width="7.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="7.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="7.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>REG_DESC</t>
+        </is>
+      </c>
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>22</v>
@@ -863,8 +842,10 @@
       <c r="G1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FIELD_DESC</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -874,14 +855,11 @@
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="1">
-        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>27</v>
@@ -897,14 +875,11 @@
       <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E3" s="1">
-        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>34</v>
@@ -916,14 +891,11 @@
     <row r="4" spans="1:8">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" s="1">
-        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>27</v>
@@ -935,14 +907,11 @@
     <row r="5" spans="1:8">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" s="1">
-        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>34</v>
@@ -954,14 +923,11 @@
     <row r="6" spans="1:8">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E6" s="1">
-        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>27</v>
@@ -977,14 +943,11 @@
       <c r="B7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" s="1">
-        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>42</v>
@@ -1000,14 +963,11 @@
       <c r="B8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="1">
-        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
@@ -1023,14 +983,11 @@
       <c r="B9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E9" s="1">
-        <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>27</v>
@@ -1046,14 +1003,11 @@
       <c r="B10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E10" s="1">
-        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>27</v>
@@ -1065,14 +1019,11 @@
     <row r="11" spans="1:8">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E11" s="1">
-        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>27</v>
@@ -1088,14 +1039,11 @@
       <c r="B12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E12" s="1">
-        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>27</v>
@@ -1107,14 +1055,11 @@
     <row r="13" spans="1:8">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E13" s="1">
-        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>27</v>
@@ -1130,11 +1075,8 @@
       <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E14" s="1">
-        <v>32</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>27</v>
@@ -1150,11 +1092,8 @@
       <c r="B15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E15" s="1">
-        <v>64</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>27</v>

--- a/example.xlsx
+++ b/example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beribeli/Workarea/irgen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA98CC92-D634-614C-8090-C66DDF59DAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11FDF787-112B-D24B-B759-39C10365E53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="block1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -37,9 +38,6 @@
     <t>VERSION</t>
   </si>
   <si>
-    <t>DESCRIPTION</t>
-  </si>
-  <si>
     <t>example.com</t>
   </si>
   <si>
@@ -61,9 +59,6 @@
     <t>RANGE</t>
   </si>
   <si>
-    <t>DESCIPTION</t>
-  </si>
-  <si>
     <t>block0</t>
   </si>
   <si>
@@ -76,25 +71,10 @@
     <t>block1</t>
   </si>
   <si>
-    <t>ADDR</t>
-  </si>
-  <si>
-    <t>REG</t>
-  </si>
-  <si>
     <t>FIELD</t>
   </si>
   <si>
     <t>BIT</t>
-  </si>
-  <si>
-    <t>WIDTH</t>
-  </si>
-  <si>
-    <t>ATTRIBUTE</t>
-  </si>
-  <si>
-    <t>DEFAULT</t>
   </si>
   <si>
     <t>reg0</t>
@@ -210,6 +190,31 @@
   </si>
   <si>
     <t>rege{n}, n=range(0, 2, 8)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>REG_DESC</t>
+  </si>
+  <si>
+    <t>FIELD_DESC</t>
+  </si>
+  <si>
+    <t>DESC</t>
+  </si>
+  <si>
+    <t>ATTR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RESET</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>REG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -463,24 +468,22 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DESC</t>
-        </is>
+      <c r="E1" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -505,40 +508,38 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>DESC</t>
-        </is>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -561,73 +562,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>REG_DESC</t>
-        </is>
-      </c>
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
+      <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>FIELD_DESC</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -638,13 +635,13 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -655,13 +652,13 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -672,13 +669,13 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -687,19 +684,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -708,19 +705,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -729,19 +726,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -750,19 +747,19 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -773,13 +770,13 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -812,77 +809,73 @@
     <col min="1" max="1" width="7.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="7.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>REG_DESC</t>
-        </is>
-      </c>
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
+      <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>FIELD_DESC</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -892,13 +885,13 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -908,13 +901,13 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -924,13 +917,13 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -938,19 +931,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -958,19 +951,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -978,19 +971,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -998,19 +991,19 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1020,13 +1013,13 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1034,19 +1027,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1056,13 +1049,13 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1070,16 +1063,16 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1087,16 +1080,16 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
